--- a/ABA_mining/outputs/eval/task3/check-in/llama3.2/contrary_v1/EVAL_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/check-in/llama3.2/contrary_v1/EVAL_SUMMARY.xlsx
@@ -541,16 +541,16 @@
         <v>38</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.421053</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.595745</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4933920704845814</v>
+        <v>0.493392</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5436507936507936</v>
+        <v>0.543651</v>
       </c>
     </row>
     <row r="3">
@@ -600,16 +600,16 @@
         <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>0.417910447761194</v>
+        <v>0.41791</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.595745</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4912280701754387</v>
+        <v>0.491228</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5396825396825397</v>
+        <v>0.539683</v>
       </c>
     </row>
     <row r="4">
@@ -659,16 +659,16 @@
         <v>38</v>
       </c>
       <c r="L4" t="n">
-        <v>0.417910447761194</v>
+        <v>0.41791</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.595745</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4912280701754387</v>
+        <v>0.491228</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5396825396825397</v>
+        <v>0.539683</v>
       </c>
     </row>
   </sheetData>
@@ -784,16 +784,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.4189526184538653</v>
+        <v>0.418953</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.595745</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4919472913616398</v>
+        <v>0.491947</v>
       </c>
       <c r="I2" t="n">
-        <v>0.541005291005291</v>
+        <v>0.541005</v>
       </c>
       <c r="J2" t="n">
         <v>756</v>
